--- a/01_Thermal/B_results/four_var_params.xlsx
+++ b/01_Thermal/B_results/four_var_params.xlsx
@@ -516,49 +516,49 @@
         <v>0.2</v>
       </c>
       <c r="B2" t="n">
-        <v>10.28556846592443</v>
+        <v>5.680987937072524</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4080557081308278</v>
+        <v>0.4994159230013621</v>
       </c>
       <c r="D2" t="n">
-        <v>0.325111012522858</v>
+        <v>0.06037192179767623</v>
       </c>
       <c r="E2" t="n">
-        <v>10.83367313134013</v>
+        <v>5.571211599582258</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3567605645627088</v>
+        <v>0.527689107287226</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4167399660415153</v>
+        <v>-0.02522067960204988</v>
       </c>
       <c r="H2" t="n">
-        <v>13.50328386093052</v>
+        <v>4.973965333054521</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3040139285325395</v>
+        <v>0.4805312792794015</v>
       </c>
       <c r="J2" t="n">
-        <v>0.3316096114966853</v>
+        <v>-0.01409076816750487</v>
       </c>
       <c r="K2" t="n">
-        <v>8.47599940733207</v>
+        <v>6.617708199902131</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5041039067600058</v>
+        <v>0.50361532866234</v>
       </c>
       <c r="M2" t="n">
-        <v>0.312764233736723</v>
+        <v>0.1386318418006026</v>
       </c>
       <c r="N2" t="n">
-        <v>8.329317464095009</v>
+        <v>5.561066615751187</v>
       </c>
       <c r="O2" t="n">
-        <v>0.4673444326680572</v>
+        <v>0.4858279767764809</v>
       </c>
       <c r="P2" t="n">
-        <v>0.2393302388165083</v>
+        <v>0.142167293159657</v>
       </c>
     </row>
     <row r="3">
@@ -566,49 +566,49 @@
         <v>0.35</v>
       </c>
       <c r="B3" t="n">
-        <v>3.511346309295957</v>
+        <v>3.018107888895867</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7505285367315629</v>
+        <v>0.7425085823731143</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1330205493927246</v>
+        <v>0.01706373521715611</v>
       </c>
       <c r="E3" t="n">
-        <v>3.214115092382382</v>
+        <v>2.545130416834025</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7710472718088488</v>
+        <v>0.8330729441941661</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1518848506470382</v>
+        <v>0.05751048110919436</v>
       </c>
       <c r="H3" t="n">
-        <v>3.401721253283312</v>
+        <v>4.157752683462951</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7555444561648517</v>
+        <v>0.61023324117227</v>
       </c>
       <c r="J3" t="n">
-        <v>0.04126782657801372</v>
+        <v>-0.04649896145691504</v>
       </c>
       <c r="K3" t="n">
-        <v>2.369831895829392</v>
+        <v>2.886967149841117</v>
       </c>
       <c r="L3" t="n">
-        <v>0.9177307567531343</v>
+        <v>0.6546373312377662</v>
       </c>
       <c r="M3" t="n">
-        <v>0.07320709031050827</v>
+        <v>-0.01462504259165151</v>
       </c>
       <c r="N3" t="n">
-        <v>5.059716995688742</v>
+        <v>2.482581305445374</v>
       </c>
       <c r="O3" t="n">
-        <v>0.5577916621994169</v>
+        <v>0.8720908128882552</v>
       </c>
       <c r="P3" t="n">
-        <v>0.2657224300353383</v>
+        <v>0.07186846380799664</v>
       </c>
     </row>
     <row r="4">
@@ -616,49 +616,49 @@
         <v>0.5</v>
       </c>
       <c r="B4" t="n">
-        <v>3.096271175227074</v>
+        <v>2.716816177795779</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7136616466309362</v>
+        <v>0.7143376832538797</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1395372256056855</v>
+        <v>0.03150455752243764</v>
       </c>
       <c r="E4" t="n">
-        <v>2.408479330691634</v>
+        <v>1.974573821865497</v>
       </c>
       <c r="F4" t="n">
-        <v>0.848306561390536</v>
+        <v>0.8511636439121998</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1172889746963408</v>
+        <v>0.01394299358898653</v>
       </c>
       <c r="H4" t="n">
-        <v>3.268338118457318</v>
+        <v>2.955432183163272</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6682234199052643</v>
+        <v>0.6496025282951642</v>
       </c>
       <c r="J4" t="n">
-        <v>0.04709625205567355</v>
+        <v>-0.06634707954893339</v>
       </c>
       <c r="K4" t="n">
-        <v>3.71496195777508</v>
+        <v>2.986518034717086</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7384063038829888</v>
+        <v>0.6895253347633158</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1522606905328895</v>
+        <v>0.05826639327326158</v>
       </c>
       <c r="N4" t="n">
-        <v>2.993305293984262</v>
+        <v>2.950740671437261</v>
       </c>
       <c r="O4" t="n">
-        <v>0.5997103013449556</v>
+        <v>0.6670592260448389</v>
       </c>
       <c r="P4" t="n">
-        <v>0.241502985137838</v>
+        <v>0.1201559227764358</v>
       </c>
     </row>
     <row r="5">
@@ -666,49 +666,49 @@
         <v>0.75</v>
       </c>
       <c r="B5" t="n">
-        <v>2.096421081335943</v>
+        <v>2.175361366374465</v>
       </c>
       <c r="C5" t="n">
-        <v>0.9252391036065621</v>
+        <v>0.8455170419653861</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1539455274756758</v>
+        <v>0.02998298755819676</v>
       </c>
       <c r="E5" t="n">
-        <v>2.044590746637241</v>
+        <v>1.699396416308604</v>
       </c>
       <c r="F5" t="n">
-        <v>1.022717721840484</v>
+        <v>0.9506038200576753</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05470347705958049</v>
+        <v>-0.407806892056287</v>
       </c>
       <c r="H5" t="n">
-        <v>1.578105127011739</v>
+        <v>1.916434587673981</v>
       </c>
       <c r="I5" t="n">
-        <v>0.9924580233453124</v>
+        <v>0.8145732002995604</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1407274660793313</v>
+        <v>-0.383298853074315</v>
       </c>
       <c r="K5" t="n">
-        <v>2.923556204047783</v>
+        <v>3.130712158447029</v>
       </c>
       <c r="L5" t="n">
-        <v>0.8817390681216822</v>
+        <v>0.6843110196072978</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1170512274066656</v>
+        <v>0.4193742714920129</v>
       </c>
       <c r="N5" t="n">
-        <v>1.839432247647009</v>
+        <v>1.954902303068244</v>
       </c>
       <c r="O5" t="n">
-        <v>0.8040416011187694</v>
+        <v>0.9325801278970108</v>
       </c>
       <c r="P5" t="n">
-        <v>0.3032999393571258</v>
+        <v>0.4916634238713762</v>
       </c>
     </row>
     <row r="6">
@@ -716,49 +716,49 @@
         <v>1.1</v>
       </c>
       <c r="B6" t="n">
-        <v>2.144815841489149</v>
+        <v>1.970391026744906</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9178077209271092</v>
+        <v>0.8998460853134932</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1306087472302757</v>
+        <v>0.02252644167990432</v>
       </c>
       <c r="E6" t="n">
-        <v>2.44793299570848</v>
+        <v>2.100988231650653</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9406073936747726</v>
+        <v>0.9183539180689477</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1433368194353746</v>
+        <v>0.009747928491490893</v>
       </c>
       <c r="H6" t="n">
-        <v>2.495430714410505</v>
+        <v>1.993554609739835</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8572564317736008</v>
+        <v>0.9315556864486312</v>
       </c>
       <c r="J6" t="n">
-        <v>0.04745521775928955</v>
+        <v>-0.0874747346643337</v>
       </c>
       <c r="K6" t="n">
-        <v>1.638415283030004</v>
+        <v>1.581220302997808</v>
       </c>
       <c r="L6" t="n">
-        <v>1.086353851502831</v>
+        <v>1.040169373278407</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1412310297398173</v>
+        <v>0.0262010085187052</v>
       </c>
       <c r="N6" t="n">
-        <v>1.997484372807609</v>
+        <v>2.205800962591327</v>
       </c>
       <c r="O6" t="n">
-        <v>0.7870132067572315</v>
+        <v>0.7093053634579866</v>
       </c>
       <c r="P6" t="n">
-        <v>0.1904119219866213</v>
+        <v>0.1416315643737549</v>
       </c>
     </row>
     <row r="7">
@@ -766,49 +766,49 @@
         <v>1.6</v>
       </c>
       <c r="B7" t="n">
-        <v>1.515628152384302</v>
+        <v>1.681549172224897</v>
       </c>
       <c r="C7" t="n">
-        <v>0.892748615629874</v>
+        <v>0.8843226221514159</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1801812119594934</v>
+        <v>0.0227466818546561</v>
       </c>
       <c r="E7" t="n">
-        <v>1.968692322355293</v>
+        <v>2.014591019681271</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8799039332139661</v>
+        <v>0.8308077542828107</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1324815627638999</v>
+        <v>-0.08538876926928325</v>
       </c>
       <c r="H7" t="n">
-        <v>1.558239747554073</v>
+        <v>1.422670391886596</v>
       </c>
       <c r="I7" t="n">
-        <v>1.18708189136354</v>
+        <v>1.073203338641863</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.01391174100679857</v>
+        <v>-0.1290225332130815</v>
       </c>
       <c r="K7" t="n">
-        <v>1.181129998307525</v>
+        <v>1.44569709991547</v>
       </c>
       <c r="L7" t="n">
-        <v>0.8381829649897526</v>
+        <v>0.8762696569691598</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2700684984391823</v>
+        <v>0.1252149514537185</v>
       </c>
       <c r="N7" t="n">
-        <v>1.354450541320318</v>
+        <v>1.84323817741625</v>
       </c>
       <c r="O7" t="n">
-        <v>0.6658256729522369</v>
+        <v>0.7570097387118303</v>
       </c>
       <c r="P7" t="n">
-        <v>0.3320865276416901</v>
+        <v>0.1801830784472706</v>
       </c>
     </row>
     <row r="8">
@@ -816,49 +816,49 @@
         <v>2.2</v>
       </c>
       <c r="B8" t="n">
-        <v>1.023440010884702</v>
+        <v>1.107345606610362</v>
       </c>
       <c r="C8" t="n">
-        <v>1.07473169769869</v>
+        <v>1.012445610696752</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2214939708620011</v>
+        <v>0.03130402284338605</v>
       </c>
       <c r="E8" t="n">
-        <v>1.149776848084294</v>
+        <v>1.069009874118248</v>
       </c>
       <c r="F8" t="n">
         <v>1.2</v>
       </c>
       <c r="G8" t="n">
-        <v>0.2740922924757421</v>
+        <v>0.06882684723762102</v>
       </c>
       <c r="H8" t="n">
-        <v>0.985416913196689</v>
+        <v>0.9633498636319099</v>
       </c>
       <c r="I8" t="n">
         <v>1.2</v>
       </c>
       <c r="J8" t="n">
-        <v>0.09431744629601729</v>
+        <v>-0.04208732149401131</v>
       </c>
       <c r="K8" t="n">
-        <v>1.293179466525437</v>
+        <v>1.184255965100813</v>
       </c>
       <c r="L8" t="n">
-        <v>1.071015642193447</v>
+        <v>0.975082552013408</v>
       </c>
       <c r="M8" t="n">
-        <v>0.193010054496031</v>
+        <v>-0.05464463242059154</v>
       </c>
       <c r="N8" t="n">
-        <v>0.6653868157323869</v>
+        <v>1.212766723590475</v>
       </c>
       <c r="O8" t="n">
-        <v>0.8279111486013149</v>
+        <v>0.6746998907736</v>
       </c>
       <c r="P8" t="n">
-        <v>0.324556090180214</v>
+        <v>0.153121198050526</v>
       </c>
     </row>
   </sheetData>
@@ -872,7 +872,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:N5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -918,25 +918,30 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>metric_scope</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>inner_bins_to_ignore</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>profile_delta_r_m</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>overlap_ratio_threshold</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>overlap_weight_power</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>overlap_sigma_boost</t>
         </is>
@@ -963,27 +968,32 @@
         <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3639761228835757</v>
+        <v>0.3397452662940638</v>
       </c>
       <c r="G2" t="n">
-        <v>146.4163414053804</v>
+        <v>131.1086722569025</v>
       </c>
       <c r="H2" t="n">
         <v>357</v>
       </c>
-      <c r="I2" t="n">
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>nearest_region_overlap_model</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
         <v>1</v>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>0.3</v>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>1.1</v>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>3</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1001,34 +1011,39 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>cauchy</t>
+          <t>soft_l1</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>1.110581394691709</v>
+        <v>0.8219870843121163</v>
       </c>
       <c r="G3" t="n">
-        <v>124.0324633633799</v>
+        <v>114.6417392171701</v>
       </c>
       <c r="H3" t="n">
         <v>315</v>
       </c>
-      <c r="I3" t="n">
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>nearest_region_overlap_model</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
         <v>1</v>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>0.3</v>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>1.1</v>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>3</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1046,34 +1061,39 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>cauchy</t>
+          <t>soft_l1</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6136024319379209</v>
+        <v>0.571177622544997</v>
       </c>
       <c r="G4" t="n">
-        <v>152.9030952902698</v>
+        <v>138.7569874446097</v>
       </c>
       <c r="H4" t="n">
         <v>371</v>
       </c>
-      <c r="I4" t="n">
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>nearest_region_overlap_model</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
         <v>1</v>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>0.3</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>1.1</v>
       </c>
-      <c r="L4" t="n">
+      <c r="M4" t="n">
         <v>3</v>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1091,34 +1111,39 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>cauchy</t>
+          <t>soft_l1</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4244879844084003</v>
+        <v>0.4047110378067769</v>
       </c>
       <c r="G5" t="n">
-        <v>127.0326734692962</v>
+        <v>124.8718400224191</v>
       </c>
       <c r="H5" t="n">
         <v>322</v>
       </c>
-      <c r="I5" t="n">
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>nearest_region_overlap_model</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
         <v>1</v>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>0.3</v>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
         <v>1.1</v>
       </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
         <v>3</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>1</v>
       </c>
     </row>

--- a/01_Thermal/B_results/four_var_params.xlsx
+++ b/01_Thermal/B_results/four_var_params.xlsx
@@ -516,49 +516,49 @@
         <v>0.2</v>
       </c>
       <c r="B2" t="n">
-        <v>5.680987937072524</v>
+        <v>6.089984553739654</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4994159230013621</v>
+        <v>0.4905950816916236</v>
       </c>
       <c r="D2" t="n">
-        <v>0.06037192179767623</v>
+        <v>0.06191890156730816</v>
       </c>
       <c r="E2" t="n">
-        <v>5.571211599582258</v>
+        <v>6.288203057546792</v>
       </c>
       <c r="F2" t="n">
-        <v>0.527689107287226</v>
+        <v>0.495686342345629</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.02522067960204988</v>
+        <v>-0.01770404722948395</v>
       </c>
       <c r="H2" t="n">
-        <v>4.973965333054521</v>
+        <v>5.915740308639087</v>
       </c>
       <c r="I2" t="n">
-        <v>0.4805312792794015</v>
+        <v>0.4798545002593161</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.01409076816750487</v>
+        <v>-0.006750504585253704</v>
       </c>
       <c r="K2" t="n">
-        <v>6.617708199902131</v>
+        <v>6.364166569550182</v>
       </c>
       <c r="L2" t="n">
-        <v>0.50361532866234</v>
+        <v>0.5116392006803203</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1386318418006026</v>
+        <v>0.1343520507481666</v>
       </c>
       <c r="N2" t="n">
-        <v>5.561066615751187</v>
+        <v>5.791828279222558</v>
       </c>
       <c r="O2" t="n">
-        <v>0.4858279767764809</v>
+        <v>0.4752002834812291</v>
       </c>
       <c r="P2" t="n">
-        <v>0.142167293159657</v>
+        <v>0.1377781073358036</v>
       </c>
     </row>
     <row r="3">
@@ -566,49 +566,49 @@
         <v>0.35</v>
       </c>
       <c r="B3" t="n">
-        <v>3.018107888895867</v>
+        <v>2.590990713058932</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7425085823731143</v>
+        <v>0.7796530094824</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01706373521715611</v>
+        <v>0.02044012428254285</v>
       </c>
       <c r="E3" t="n">
-        <v>2.545130416834025</v>
+        <v>2.784583639480507</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8330729441941661</v>
+        <v>0.7508051693892465</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05751048110919436</v>
+        <v>0.1052623837038618</v>
       </c>
       <c r="H3" t="n">
-        <v>4.157752683462951</v>
+        <v>2.345345035519149</v>
       </c>
       <c r="I3" t="n">
-        <v>0.61023324117227</v>
+        <v>0.8185364775605404</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.04649896145691504</v>
+        <v>-0.08888747219118059</v>
       </c>
       <c r="K3" t="n">
-        <v>2.886967149841117</v>
+        <v>2.940084704258748</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6546373312377662</v>
+        <v>0.6938061773642237</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.01462504259165151</v>
+        <v>-0.06840656189335079</v>
       </c>
       <c r="N3" t="n">
-        <v>2.482581305445374</v>
+        <v>2.293949472977327</v>
       </c>
       <c r="O3" t="n">
-        <v>0.8720908128882552</v>
+        <v>0.8554642136155898</v>
       </c>
       <c r="P3" t="n">
-        <v>0.07186846380799664</v>
+        <v>0.133792147510841</v>
       </c>
     </row>
     <row r="4">
@@ -616,49 +616,49 @@
         <v>0.5</v>
       </c>
       <c r="B4" t="n">
-        <v>2.716816177795779</v>
+        <v>2.712432876171878</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7143376832538797</v>
+        <v>0.6930135884507107</v>
       </c>
       <c r="D4" t="n">
-        <v>0.03150455752243764</v>
+        <v>0.04032615421418319</v>
       </c>
       <c r="E4" t="n">
-        <v>1.974573821865497</v>
+        <v>2.024925761515862</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8511636439121998</v>
+        <v>0.8037768197923161</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01394299358898653</v>
+        <v>0.01940833323942311</v>
       </c>
       <c r="H4" t="n">
-        <v>2.955432183163272</v>
+        <v>2.995967339240817</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6496025282951642</v>
+        <v>0.6295174587448237</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.06634707954893339</v>
+        <v>-0.04890275581653087</v>
       </c>
       <c r="K4" t="n">
-        <v>2.986518034717086</v>
+        <v>2.857687829124438</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6895253347633158</v>
+        <v>0.6873861179802738</v>
       </c>
       <c r="M4" t="n">
-        <v>0.05826639327326158</v>
+        <v>0.06409551827229576</v>
       </c>
       <c r="N4" t="n">
-        <v>2.950740671437261</v>
+        <v>2.971150574806396</v>
       </c>
       <c r="O4" t="n">
-        <v>0.6670592260448389</v>
+        <v>0.6513739572854294</v>
       </c>
       <c r="P4" t="n">
-        <v>0.1201559227764358</v>
+        <v>0.1267035211615448</v>
       </c>
     </row>
     <row r="5">
@@ -666,49 +666,49 @@
         <v>0.75</v>
       </c>
       <c r="B5" t="n">
-        <v>2.175361366374465</v>
+        <v>2.200196258551008</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8455170419653861</v>
+        <v>0.8247055888652535</v>
       </c>
       <c r="D5" t="n">
-        <v>0.02998298755819676</v>
+        <v>0.03532324719417668</v>
       </c>
       <c r="E5" t="n">
-        <v>1.699396416308604</v>
+        <v>1.730771068564759</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9506038200576753</v>
+        <v>0.9059995928811008</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.407806892056287</v>
+        <v>-0.07480474550941366</v>
       </c>
       <c r="H5" t="n">
-        <v>1.916434587673981</v>
+        <v>1.91284138618197</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8145732002995604</v>
+        <v>0.8279948457743814</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.383298853074315</v>
+        <v>-0.01386864359711243</v>
       </c>
       <c r="K5" t="n">
-        <v>3.130712158447029</v>
+        <v>2.822868245458011</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6843110196072978</v>
+        <v>0.7320375419633468</v>
       </c>
       <c r="M5" t="n">
-        <v>0.4193742714920129</v>
+        <v>0.08139701269390449</v>
       </c>
       <c r="N5" t="n">
-        <v>1.954902303068244</v>
+        <v>2.334304333999293</v>
       </c>
       <c r="O5" t="n">
-        <v>0.9325801278970108</v>
+        <v>0.8327903748421849</v>
       </c>
       <c r="P5" t="n">
-        <v>0.4916634238713762</v>
+        <v>0.1485693651893283</v>
       </c>
     </row>
     <row r="6">
@@ -716,49 +716,49 @@
         <v>1.1</v>
       </c>
       <c r="B6" t="n">
-        <v>1.970391026744906</v>
+        <v>1.961755795654303</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8998460853134932</v>
+        <v>0.8826239081779494</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02252644167990432</v>
+        <v>0.02988406223369677</v>
       </c>
       <c r="E6" t="n">
-        <v>2.100988231650653</v>
+        <v>2.074620298494775</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9183539180689477</v>
+        <v>0.9201902602193599</v>
       </c>
       <c r="G6" t="n">
-        <v>0.009747928491490893</v>
+        <v>0.04787972262869446</v>
       </c>
       <c r="H6" t="n">
-        <v>1.993554609739835</v>
+        <v>2.146632833424312</v>
       </c>
       <c r="I6" t="n">
-        <v>0.9315556864486312</v>
+        <v>0.8595031251700745</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.0874747346643337</v>
+        <v>-0.1637410012844519</v>
       </c>
       <c r="K6" t="n">
-        <v>1.581220302997808</v>
+        <v>1.589618583548406</v>
       </c>
       <c r="L6" t="n">
-        <v>1.040169373278407</v>
+        <v>1.018167864697904</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0262010085187052</v>
+        <v>0.05968906158448587</v>
       </c>
       <c r="N6" t="n">
-        <v>2.205800962591327</v>
+        <v>2.036151467149718</v>
       </c>
       <c r="O6" t="n">
-        <v>0.7093053634579866</v>
+        <v>0.7326343826244587</v>
       </c>
       <c r="P6" t="n">
-        <v>0.1416315643737549</v>
+        <v>0.1757084660060586</v>
       </c>
     </row>
     <row r="7">
@@ -766,49 +766,49 @@
         <v>1.6</v>
       </c>
       <c r="B7" t="n">
-        <v>1.681549172224897</v>
+        <v>1.692398814238913</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8843226221514159</v>
+        <v>0.8920664806928476</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0227466818546561</v>
+        <v>0.0203805591985989</v>
       </c>
       <c r="E7" t="n">
-        <v>2.014591019681271</v>
+        <v>2.066394125986438</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8308077542828107</v>
+        <v>0.821516303442391</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.08538876926928325</v>
+        <v>-0.08971426416148973</v>
       </c>
       <c r="H7" t="n">
-        <v>1.422670391886596</v>
+        <v>1.40066126425859</v>
       </c>
       <c r="I7" t="n">
-        <v>1.073203338641863</v>
+        <v>1.098905519229643</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.1290225332130815</v>
+        <v>-0.1331416697785585</v>
       </c>
       <c r="K7" t="n">
-        <v>1.44569709991547</v>
+        <v>1.463930737527172</v>
       </c>
       <c r="L7" t="n">
-        <v>0.8762696569691598</v>
+        <v>0.8832203774771423</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1252149514537185</v>
+        <v>0.1247206712468533</v>
       </c>
       <c r="N7" t="n">
-        <v>1.84323817741625</v>
+        <v>1.83860912918345</v>
       </c>
       <c r="O7" t="n">
-        <v>0.7570097387118303</v>
+        <v>0.7646237226222141</v>
       </c>
       <c r="P7" t="n">
-        <v>0.1801830784472706</v>
+        <v>0.1796574994875905</v>
       </c>
     </row>
     <row r="8">
@@ -816,49 +816,49 @@
         <v>2.2</v>
       </c>
       <c r="B8" t="n">
-        <v>1.107345606610362</v>
+        <v>1.110603149290837</v>
       </c>
       <c r="C8" t="n">
-        <v>1.012445610696752</v>
+        <v>1.006027825308475</v>
       </c>
       <c r="D8" t="n">
-        <v>0.03130402284338605</v>
+        <v>0.03303174228086334</v>
       </c>
       <c r="E8" t="n">
-        <v>1.069009874118248</v>
+        <v>1.068786731577523</v>
       </c>
       <c r="F8" t="n">
         <v>1.2</v>
       </c>
       <c r="G8" t="n">
-        <v>0.06882684723762102</v>
+        <v>0.06716456637058453</v>
       </c>
       <c r="H8" t="n">
-        <v>0.9633498636319099</v>
+        <v>0.9844486280135063</v>
       </c>
       <c r="I8" t="n">
         <v>1.2</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.04208732149401131</v>
+        <v>-0.03675135584926886</v>
       </c>
       <c r="K8" t="n">
-        <v>1.184255965100813</v>
+        <v>1.194185865923956</v>
       </c>
       <c r="L8" t="n">
-        <v>0.975082552013408</v>
+        <v>0.9484390532410482</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.05464463242059154</v>
+        <v>-0.05010678866475023</v>
       </c>
       <c r="N8" t="n">
-        <v>1.212766723590475</v>
+        <v>1.19499137164836</v>
       </c>
       <c r="O8" t="n">
-        <v>0.6746998907736</v>
+        <v>0.6756722479928523</v>
       </c>
       <c r="P8" t="n">
-        <v>0.153121198050526</v>
+        <v>0.1518205472668879</v>
       </c>
     </row>
   </sheetData>
@@ -968,10 +968,10 @@
         <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3397452662940638</v>
+        <v>0.3980801009595391</v>
       </c>
       <c r="G2" t="n">
-        <v>131.1086722569025</v>
+        <v>129.8297556693767</v>
       </c>
       <c r="H2" t="n">
         <v>357</v>
@@ -1018,10 +1018,10 @@
         <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8219870843121163</v>
+        <v>0.4400489659573123</v>
       </c>
       <c r="G3" t="n">
-        <v>114.6417392171701</v>
+        <v>116.8844902855623</v>
       </c>
       <c r="H3" t="n">
         <v>315</v>
@@ -1068,10 +1068,10 @@
         <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>0.571177622544997</v>
+        <v>0.4010278011596341</v>
       </c>
       <c r="G4" t="n">
-        <v>138.7569874446097</v>
+        <v>139.3596575139707</v>
       </c>
       <c r="H4" t="n">
         <v>371</v>
@@ -1118,10 +1118,10 @@
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4047110378067769</v>
+        <v>0.4421523663637061</v>
       </c>
       <c r="G5" t="n">
-        <v>124.8718400224191</v>
+        <v>123.2158376060535</v>
       </c>
       <c r="H5" t="n">
         <v>322</v>
